--- a/docs/downloads/经营分_鲁东省区__威烟片区_2026-10-18.xlsx
+++ b/docs/downloads/经营分_鲁东省区__威烟片区_2026-10-18.xlsx
@@ -709,7 +709,7 @@
         <v>63</v>
       </c>
       <c r="I2" t="n">
-        <v>-15</v>
+        <v>-10</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -794,10 +794,10 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="I3" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -829,7 +829,7 @@
         <v>30</v>
       </c>
       <c r="S3" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="T3" t="n">
         <v>20</v>
@@ -1298,22 +1298,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>烟台市</t>
+          <t>威海市</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>6806139847921698827</t>
+          <t>7605189072658630682</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>麗枫酒店（烟台莱阳市中心店）</t>
+          <t>锦江都城酒店（威海刘公岛幸福门店）</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>麗枫酒店(烟台莱阳市中心店)</t>
+          <t>锦江都城酒店(威海刘公岛幸福门店)</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -1329,7 +1329,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>稳房源,提质量,拿收益</t>
+          <t>稳房源,提质量,附加分,拿收益</t>
         </is>
       </c>
       <c r="K9" t="n">
@@ -1351,13 +1351,13 @@
         <v>30</v>
       </c>
       <c r="Q9" t="n">
+        <v>20</v>
+      </c>
+      <c r="R9" t="n">
+        <v>30</v>
+      </c>
+      <c r="S9" t="n">
         <v>15</v>
-      </c>
-      <c r="R9" t="n">
-        <v>30</v>
-      </c>
-      <c r="S9" t="n">
-        <v>20</v>
       </c>
       <c r="T9" t="n">
         <v>20</v>
@@ -1386,22 +1386,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>威海市</t>
+          <t>烟台市</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>6892229294085376015</t>
+          <t>6806139847921698827</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>潮漫酒店（威海乳山人民广场青山路店）</t>
+          <t>麗枫酒店（烟台莱阳市中心店）</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>潮漫酒店(威海乳山人民广场青山路店)</t>
+          <t>麗枫酒店(烟台莱阳市中心店)</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -1410,7 +1410,7 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
@@ -1427,19 +1427,19 @@
         <v>10</v>
       </c>
       <c r="M10" t="n">
+        <v>22</v>
+      </c>
+      <c r="N10" t="n">
+        <v>30</v>
+      </c>
+      <c r="O10" t="n">
+        <v>20</v>
+      </c>
+      <c r="P10" t="n">
+        <v>30</v>
+      </c>
+      <c r="Q10" t="n">
         <v>15</v>
-      </c>
-      <c r="N10" t="n">
-        <v>30</v>
-      </c>
-      <c r="O10" t="n">
-        <v>25</v>
-      </c>
-      <c r="P10" t="n">
-        <v>30</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>20</v>
       </c>
       <c r="R10" t="n">
         <v>30</v>
@@ -1479,29 +1479,29 @@
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>7513387116722653210</t>
+          <t>6892229294085376015</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>希岸酒店（威海北站火炬八街海水浴场店）</t>
+          <t>潮漫酒店（威海乳山人民广场青山路店）</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>希岸酒店(威海北站火炬八街海水浴场店)</t>
+          <t>潮漫酒店(威海乳山人民广场青山路店)</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>未认证</t>
+          <t>已认证</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="I11" t="n">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
@@ -1515,7 +1515,7 @@
         <v>10</v>
       </c>
       <c r="M11" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="N11" t="n">
         <v>30</v>
@@ -1527,7 +1527,7 @@
         <v>30</v>
       </c>
       <c r="Q11" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="R11" t="n">
         <v>30</v>
@@ -1567,17 +1567,17 @@
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>7229952617135212600</t>
+          <t>7513387116722653210</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>希岸酒店（威海高铁站九龙湾公园店）</t>
+          <t>希岸酒店（威海北站火炬八街海水浴场店）</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>希岸酒店(威海高铁站韩乐坊九龙城店)</t>
+          <t>希岸酒店(威海北站火炬八街海水浴场店)</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1589,7 +1589,7 @@
         <v>92</v>
       </c>
       <c r="I12" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
@@ -1655,17 +1655,17 @@
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>6601137413152573453</t>
+          <t>7229952617135212600</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>维也纳国际酒店（威海荣成高铁站店）</t>
+          <t>希岸酒店（威海高铁站九龙湾公园店）</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>维也纳国际酒店(荣成店)</t>
+          <t>希岸酒店(威海高铁站韩乐坊九龙城店)</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -1677,7 +1677,7 @@
         <v>92</v>
       </c>
       <c r="I13" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -1743,17 +1743,17 @@
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>6683260110866876429</t>
+          <t>6601137413152573453</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>维也纳酒店（威海高铁站韩乐坊华夏城店）</t>
+          <t>维也纳国际酒店（威海荣成高铁站店）</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>维也纳酒店(威海高铁站华夏城海上公园店)</t>
+          <t>维也纳国际酒店(荣成店)</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -1765,7 +1765,7 @@
         <v>92</v>
       </c>
       <c r="I14" t="n">
-        <v>-3</v>
+        <v>5</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
@@ -1785,13 +1785,13 @@
         <v>30</v>
       </c>
       <c r="O14" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="P14" t="n">
         <v>30</v>
       </c>
       <c r="Q14" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="R14" t="n">
         <v>30</v>
@@ -1831,17 +1831,17 @@
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>7605189072658630682</t>
+          <t>6683260110866876429</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>锦江都城酒店（威海刘公岛幸福门店）</t>
+          <t>维也纳酒店（威海高铁站韩乐坊华夏城店）</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>锦江都城酒店(威海刘公岛幸福门店)</t>
+          <t>维也纳酒店(威海高铁站华夏城海上公园店)</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -1853,11 +1853,11 @@
         <v>92</v>
       </c>
       <c r="I15" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>稳房源,提质量,附加分,拿收益</t>
+          <t>稳房源,提质量,拿收益</t>
         </is>
       </c>
       <c r="K15" t="n">
@@ -1873,7 +1873,7 @@
         <v>30</v>
       </c>
       <c r="O15" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="P15" t="n">
         <v>30</v>
@@ -1885,7 +1885,7 @@
         <v>30</v>
       </c>
       <c r="S15" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T15" t="n">
         <v>20</v>
@@ -2550,7 +2550,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>已认证</t>
+          <t>未认证</t>
         </is>
       </c>
       <c r="H23" t="n">
@@ -2638,7 +2638,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>未认证</t>
+          <t>已认证</t>
         </is>
       </c>
       <c r="H24" t="n">
@@ -2821,7 +2821,7 @@
         <v>100</v>
       </c>
       <c r="I26" t="n">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="J26" t="inlineStr">
         <is>
@@ -3261,7 +3261,7 @@
         <v>102</v>
       </c>
       <c r="I31" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J31" t="inlineStr">
         <is>
@@ -3789,7 +3789,7 @@
         <v>110</v>
       </c>
       <c r="I37" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="J37" t="inlineStr">
         <is>
